--- a/RetailSense - Sales Intelligence & Analytics Dashboard.xlsx
+++ b/RetailSense - Sales Intelligence & Analytics Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Excel\Final PR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC2B53F-B5EE-4DF9-A753-723C31AC4A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01EADAC-AC8F-472C-BFEE-9126C8E13C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2154,6 +2154,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2175,16 +2187,13 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2194,15 +2203,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -18869,7 +18869,7 @@
     <dataField name="Sum of Total_Amount" fld="13" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="3">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -19169,7 +19169,7 @@
     <dataField name="Sum of Total_Amount" fld="13" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="1">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -19422,6 +19422,134 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C98FC8E-9537-4E59-9DE5-AE59352D3D33}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A2:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total_Amount" fld="13" baseField="0" baseItem="0" numFmtId="167"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E75B5CEC-3492-4A81-93D3-90F0F8BC5324}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="5">
   <location ref="A39:B43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
@@ -19475,7 +19603,7 @@
     <dataField name="Sum of Total_Amount" fld="13" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="2">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -19673,7 +19801,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8425959B-9C09-4A9F-A609-E2A737DFAB87}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="5">
   <location ref="A17:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
@@ -19767,135 +19895,7 @@
     <dataField name="Sum of Total_Amount" fld="13" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C98FC8E-9537-4E59-9DE5-AE59352D3D33}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A2:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total_Amount" fld="13" baseField="0" baseItem="0" numFmtId="167"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="4">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -20243,22 +20243,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="72" t="s">
         <v>454</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
       <c r="O1" s="23"/>
       <c r="P1" s="23"/>
       <c r="Q1" s="23"/>
@@ -20269,20 +20269,20 @@
       <c r="V1" s="23"/>
     </row>
     <row r="2" spans="1:22" ht="15" customHeight="1">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
       <c r="Q2" s="23"/>
@@ -20293,20 +20293,20 @@
       <c r="V2" s="23"/>
     </row>
     <row r="3" spans="1:22" ht="15" customHeight="1">
-      <c r="A3" s="80"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
       <c r="Q3" s="23"/>
@@ -20317,20 +20317,20 @@
       <c r="V3" s="23"/>
     </row>
     <row r="4" spans="1:22" ht="15" customHeight="1">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="80"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="80"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="72"/>
       <c r="O4" s="23"/>
       <c r="P4" s="23"/>
       <c r="Q4" s="23"/>
@@ -20341,13 +20341,13 @@
       <c r="V4" s="23"/>
     </row>
     <row r="5" spans="1:22">
-      <c r="G5" s="82" t="s">
+      <c r="G5" s="74" t="s">
         <v>455</v>
       </c>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82"/>
-      <c r="K5" s="82"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
     </row>
     <row r="6" spans="1:22">
       <c r="G6" s="25" t="s">
@@ -20359,10 +20359,10 @@
       <c r="I6" s="25" t="s">
         <v>458</v>
       </c>
-      <c r="J6" s="82" t="s">
+      <c r="J6" s="74" t="s">
         <v>459</v>
       </c>
-      <c r="K6" s="82"/>
+      <c r="K6" s="74"/>
     </row>
     <row r="7" spans="1:22">
       <c r="G7" s="25" t="s">
@@ -20375,11 +20375,11 @@
       <c r="I7" s="26">
         <v>200000</v>
       </c>
-      <c r="J7" s="81" t="str">
+      <c r="J7" s="73" t="str">
         <f>IF(H7&gt;=I7,"✅ On Target","❌ Below Target")</f>
         <v>✅ On Target</v>
       </c>
-      <c r="K7" s="81"/>
+      <c r="K7" s="73"/>
     </row>
     <row r="8" spans="1:22">
       <c r="G8" s="25" t="s">
@@ -20392,11 +20392,11 @@
       <c r="I8" s="26">
         <v>800</v>
       </c>
-      <c r="J8" s="81" t="str">
+      <c r="J8" s="73" t="str">
         <f>IF(H8&gt;=I8,"✅ On Target","❌ Below Target")</f>
         <v>✅ On Target</v>
       </c>
-      <c r="K8" s="81"/>
+      <c r="K8" s="73"/>
     </row>
     <row r="9" spans="1:22">
       <c r="G9" s="25" t="s">
@@ -20409,11 +20409,11 @@
       <c r="I9" s="24">
         <v>200</v>
       </c>
-      <c r="J9" s="81" t="str">
+      <c r="J9" s="73" t="str">
         <f>IF(H9&gt;=I9,"✅ On Target","❌ Below Target")</f>
         <v>✅ On Target</v>
       </c>
-      <c r="K9" s="81"/>
+      <c r="K9" s="73"/>
     </row>
     <row r="10" spans="1:22">
       <c r="G10" s="25" t="s">
@@ -20426,11 +20426,11 @@
       <c r="I10" s="24">
         <v>45</v>
       </c>
-      <c r="J10" s="81" t="str">
+      <c r="J10" s="73" t="str">
         <f>IF(H10&gt;=I10,"✅ On Target","❌ Below Target")</f>
         <v>✅ On Target</v>
       </c>
-      <c r="K10" s="81"/>
+      <c r="K10" s="73"/>
     </row>
     <row r="19" spans="13:13">
       <c r="M19" s="24"/>
@@ -20442,10 +20442,10 @@
       <c r="B39" t="s">
         <v>437</v>
       </c>
-      <c r="D39" s="79" t="s">
+      <c r="D39" s="75" t="s">
         <v>453</v>
       </c>
-      <c r="E39" s="79"/>
+      <c r="E39" s="75"/>
       <c r="G39" s="3" t="s">
         <v>3</v>
       </c>
@@ -20659,10 +20659,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="77" t="s">
         <v>403</v>
       </c>
-      <c r="B1" s="73"/>
+      <c r="B1" s="77"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13" t="s">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="B3" s="15">
         <f ca="1">NOW()</f>
-        <v>46155.767109722219</v>
+        <v>46155.777151620372</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -20701,10 +20701,10 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="72" t="s">
+      <c r="A7" s="76" t="s">
         <v>408</v>
       </c>
-      <c r="B7" s="72"/>
+      <c r="B7" s="76"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="7" t="s">
@@ -20752,11 +20752,11 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="72" t="s">
+      <c r="A15" s="76" t="s">
         <v>414</v>
       </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="72"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="76"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="18" t="str" cm="1">
@@ -21426,44 +21426,44 @@
       </c>
     </row>
     <row r="69" spans="1:17">
-      <c r="A69" s="72" t="s">
+      <c r="A69" s="76" t="s">
         <v>417</v>
       </c>
-      <c r="B69" s="72"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
-      <c r="G69" s="72"/>
-      <c r="H69" s="72"/>
-      <c r="I69" s="72"/>
-      <c r="J69" s="72"/>
-      <c r="K69" s="72"/>
-      <c r="L69" s="72"/>
-      <c r="M69" s="72"/>
-      <c r="N69" s="72"/>
-      <c r="O69" s="72"/>
-      <c r="P69" s="72"/>
+      <c r="B69" s="76"/>
+      <c r="C69" s="76"/>
+      <c r="D69" s="76"/>
+      <c r="E69" s="76"/>
+      <c r="F69" s="76"/>
+      <c r="G69" s="76"/>
+      <c r="H69" s="76"/>
+      <c r="I69" s="76"/>
+      <c r="J69" s="76"/>
+      <c r="K69" s="76"/>
+      <c r="L69" s="76"/>
+      <c r="M69" s="76"/>
+      <c r="N69" s="76"/>
+      <c r="O69" s="76"/>
+      <c r="P69" s="76"/>
     </row>
     <row r="70" spans="1:17">
-      <c r="A70" s="74" t="s">
+      <c r="A70" s="78" t="s">
         <v>418</v>
       </c>
-      <c r="B70" s="75"/>
-      <c r="C70" s="75"/>
-      <c r="D70" s="75"/>
-      <c r="E70" s="75"/>
-      <c r="F70" s="75"/>
-      <c r="G70" s="75"/>
-      <c r="H70" s="75"/>
-      <c r="I70" s="75"/>
-      <c r="J70" s="75"/>
-      <c r="K70" s="75"/>
-      <c r="L70" s="75"/>
-      <c r="M70" s="75"/>
-      <c r="N70" s="75"/>
-      <c r="O70" s="75"/>
-      <c r="P70" s="76"/>
+      <c r="B70" s="79"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="79"/>
+      <c r="E70" s="79"/>
+      <c r="F70" s="79"/>
+      <c r="G70" s="79"/>
+      <c r="H70" s="79"/>
+      <c r="I70" s="79"/>
+      <c r="J70" s="79"/>
+      <c r="K70" s="79"/>
+      <c r="L70" s="79"/>
+      <c r="M70" s="79"/>
+      <c r="N70" s="79"/>
+      <c r="O70" s="79"/>
+      <c r="P70" s="80"/>
       <c r="Q70" s="1"/>
     </row>
     <row r="71" spans="1:17">
@@ -27737,11 +27737,11 @@
       </c>
     </row>
     <row r="167" spans="1:16">
-      <c r="A167" s="72" t="s">
+      <c r="A167" s="76" t="s">
         <v>419</v>
       </c>
-      <c r="B167" s="72"/>
-      <c r="C167" s="72"/>
+      <c r="B167" s="76"/>
+      <c r="C167" s="76"/>
     </row>
     <row r="168" spans="1:16">
       <c r="A168" s="21" t="s">
@@ -28229,12 +28229,12 @@
       </c>
     </row>
     <row r="211" spans="1:4">
-      <c r="A211" s="72" t="s">
+      <c r="A211" s="76" t="s">
         <v>423</v>
       </c>
-      <c r="B211" s="72"/>
-      <c r="C211" s="72"/>
-      <c r="D211" s="72"/>
+      <c r="B211" s="76"/>
+      <c r="C211" s="76"/>
+      <c r="D211" s="76"/>
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="21" t="s">
@@ -28575,10 +28575,10 @@
       </c>
     </row>
     <row r="232" spans="1:4">
-      <c r="A232" s="72" t="s">
+      <c r="A232" s="76" t="s">
         <v>428</v>
       </c>
-      <c r="B232" s="72"/>
+      <c r="B232" s="76"/>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="7" t="s">
@@ -28586,7 +28586,7 @@
       </c>
       <c r="B233" s="12">
         <f ca="1">NOW()</f>
-        <v>46155.767109722219</v>
+        <v>46155.777151620372</v>
       </c>
     </row>
   </sheetData>
@@ -28632,16 +28632,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="81" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="77"/>
+      <c r="B1" s="81"/>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="82" t="s">
         <v>431</v>
       </c>
-      <c r="B3" s="78"/>
+      <c r="B3" s="82"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="44" t="s">
@@ -28677,10 +28677,10 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="82" t="s">
         <v>478</v>
       </c>
-      <c r="B11" s="78"/>
+      <c r="B11" s="82"/>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="44" t="s">
@@ -29155,10 +29155,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="75" t="s">
         <v>436</v>
       </c>
-      <c r="B1" s="79"/>
+      <c r="B1" s="75"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
@@ -29217,10 +29217,10 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="79" t="s">
+      <c r="A16" s="75" t="s">
         <v>439</v>
       </c>
-      <c r="B16" s="79"/>
+      <c r="B16" s="75"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
@@ -29343,10 +29343,10 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="79" t="s">
+      <c r="A38" s="75" t="s">
         <v>453</v>
       </c>
-      <c r="B38" s="79"/>
+      <c r="B38" s="75"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="3" t="s">
@@ -29412,16 +29412,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" customHeight="1">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="86" t="s">
         <v>506</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="85"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="88"/>
     </row>
     <row r="2" spans="1:8" ht="14.4" customHeight="1">
       <c r="A2" s="60"/>
@@ -29434,16 +29434,16 @@
       <c r="H2" s="63"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="83" t="s">
+      <c r="A3" s="86" t="s">
         <v>507</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="85"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="88"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="61"/>
@@ -29526,16 +29526,16 @@
       <c r="H9" s="63"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="83" t="s">
+      <c r="A10" s="86" t="s">
         <v>509</v>
       </c>
-      <c r="B10" s="84"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="85"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="88"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="61"/>
@@ -29654,131 +29654,136 @@
       <c r="H17" s="63"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="88" t="s">
+      <c r="A18" s="85" t="s">
         <v>511</v>
       </c>
-      <c r="B18" s="88"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="88"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="88"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="88"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="85"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="62">
         <v>1</v>
       </c>
-      <c r="B19" s="86" t="s">
+      <c r="B19" s="83" t="s">
         <v>512</v>
       </c>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="86"/>
-      <c r="G19" s="86"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
       <c r="H19" s="63"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="62">
         <v>2</v>
       </c>
-      <c r="B20" s="86" t="s">
+      <c r="B20" s="83" t="s">
         <v>513</v>
       </c>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
       <c r="H20" s="63"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="62">
         <v>3</v>
       </c>
-      <c r="B21" s="86" t="s">
+      <c r="B21" s="83" t="s">
         <v>514</v>
       </c>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="86"/>
-      <c r="G21" s="86"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
       <c r="H21" s="63"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="62">
         <v>4</v>
       </c>
-      <c r="B22" s="86" t="s">
+      <c r="B22" s="83" t="s">
         <v>515</v>
       </c>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="86"/>
-      <c r="G22" s="86"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
       <c r="H22" s="63"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="62">
         <v>5</v>
       </c>
-      <c r="B23" s="86" t="s">
+      <c r="B23" s="83" t="s">
         <v>516</v>
       </c>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="86"/>
-      <c r="G23" s="86"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
       <c r="H23" s="63"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="62">
         <v>6</v>
       </c>
-      <c r="B24" s="86" t="s">
+      <c r="B24" s="83" t="s">
         <v>517</v>
       </c>
-      <c r="C24" s="86"/>
-      <c r="D24" s="86"/>
-      <c r="E24" s="86"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="86"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
       <c r="H24" s="63"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="62">
         <v>7</v>
       </c>
-      <c r="B25" s="86" t="s">
+      <c r="B25" s="83" t="s">
         <v>518</v>
       </c>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
       <c r="H25" s="63"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="64">
         <v>8</v>
       </c>
-      <c r="B26" s="87" t="s">
+      <c r="B26" s="84" t="s">
         <v>519</v>
       </c>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="87"/>
-      <c r="G26" s="87"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="84"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
       <c r="H26" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="A18:H18"/>
@@ -29786,11 +29791,6 @@
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B21:G21"/>
     <mergeCell ref="B22:G22"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B24:G24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/RetailSense - Sales Intelligence & Analytics Dashboard.xlsx
+++ b/RetailSense - Sales Intelligence & Analytics Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Excel\Final PR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01EADAC-AC8F-472C-BFEE-9126C8E13C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52786B4B-F31D-4A7F-8672-5A9A0B2D1ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="7" r:id="rId1"/>
@@ -1818,7 +1818,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2023,11 +2023,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2154,6 +2163,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2187,6 +2197,15 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2194,15 +2213,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -20243,22 +20253,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" customHeight="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="73" t="s">
         <v>454</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
       <c r="O1" s="23"/>
       <c r="P1" s="23"/>
       <c r="Q1" s="23"/>
@@ -20269,20 +20279,20 @@
       <c r="V1" s="23"/>
     </row>
     <row r="2" spans="1:22" ht="15" customHeight="1">
-      <c r="A2" s="72"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
       <c r="Q2" s="23"/>
@@ -20293,20 +20303,20 @@
       <c r="V2" s="23"/>
     </row>
     <row r="3" spans="1:22" ht="15" customHeight="1">
-      <c r="A3" s="72"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
+      <c r="A3" s="73"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
       <c r="Q3" s="23"/>
@@ -20317,20 +20327,20 @@
       <c r="V3" s="23"/>
     </row>
     <row r="4" spans="1:22" ht="15" customHeight="1">
-      <c r="A4" s="72"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
+      <c r="A4" s="73"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
       <c r="O4" s="23"/>
       <c r="P4" s="23"/>
       <c r="Q4" s="23"/>
@@ -20341,13 +20351,13 @@
       <c r="V4" s="23"/>
     </row>
     <row r="5" spans="1:22">
-      <c r="G5" s="74" t="s">
+      <c r="G5" s="75" t="s">
         <v>455</v>
       </c>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
     </row>
     <row r="6" spans="1:22">
       <c r="G6" s="25" t="s">
@@ -20359,10 +20369,10 @@
       <c r="I6" s="25" t="s">
         <v>458</v>
       </c>
-      <c r="J6" s="74" t="s">
+      <c r="J6" s="75" t="s">
         <v>459</v>
       </c>
-      <c r="K6" s="74"/>
+      <c r="K6" s="75"/>
     </row>
     <row r="7" spans="1:22">
       <c r="G7" s="25" t="s">
@@ -20375,11 +20385,11 @@
       <c r="I7" s="26">
         <v>200000</v>
       </c>
-      <c r="J7" s="73" t="str">
+      <c r="J7" s="74" t="str">
         <f>IF(H7&gt;=I7,"✅ On Target","❌ Below Target")</f>
         <v>✅ On Target</v>
       </c>
-      <c r="K7" s="73"/>
+      <c r="K7" s="74"/>
     </row>
     <row r="8" spans="1:22">
       <c r="G8" s="25" t="s">
@@ -20392,11 +20402,11 @@
       <c r="I8" s="26">
         <v>800</v>
       </c>
-      <c r="J8" s="73" t="str">
+      <c r="J8" s="74" t="str">
         <f>IF(H8&gt;=I8,"✅ On Target","❌ Below Target")</f>
         <v>✅ On Target</v>
       </c>
-      <c r="K8" s="73"/>
+      <c r="K8" s="74"/>
     </row>
     <row r="9" spans="1:22">
       <c r="G9" s="25" t="s">
@@ -20409,11 +20419,11 @@
       <c r="I9" s="24">
         <v>200</v>
       </c>
-      <c r="J9" s="73" t="str">
+      <c r="J9" s="74" t="str">
         <f>IF(H9&gt;=I9,"✅ On Target","❌ Below Target")</f>
         <v>✅ On Target</v>
       </c>
-      <c r="K9" s="73"/>
+      <c r="K9" s="74"/>
     </row>
     <row r="10" spans="1:22">
       <c r="G10" s="25" t="s">
@@ -20426,11 +20436,11 @@
       <c r="I10" s="24">
         <v>45</v>
       </c>
-      <c r="J10" s="73" t="str">
+      <c r="J10" s="74" t="str">
         <f>IF(H10&gt;=I10,"✅ On Target","❌ Below Target")</f>
         <v>✅ On Target</v>
       </c>
-      <c r="K10" s="73"/>
+      <c r="K10" s="74"/>
     </row>
     <row r="19" spans="13:13">
       <c r="M19" s="24"/>
@@ -20442,10 +20452,10 @@
       <c r="B39" t="s">
         <v>437</v>
       </c>
-      <c r="D39" s="75" t="s">
+      <c r="D39" s="76" t="s">
         <v>453</v>
       </c>
-      <c r="E39" s="75"/>
+      <c r="E39" s="76"/>
       <c r="G39" s="3" t="s">
         <v>3</v>
       </c>
@@ -20659,10 +20669,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>403</v>
       </c>
-      <c r="B1" s="77"/>
+      <c r="B1" s="78"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13" t="s">
@@ -20670,7 +20680,7 @@
       </c>
       <c r="B2" s="14">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -20679,7 +20689,7 @@
       </c>
       <c r="B3" s="15">
         <f ca="1">NOW()</f>
-        <v>46155.777151620372</v>
+        <v>46159.602401041666</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -20688,7 +20698,7 @@
       </c>
       <c r="B4" s="16">
         <f ca="1">DATEDIF(MIN('Raw data'!B2:B251),TODAY(),"D")</f>
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -20701,10 +20711,10 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="77" t="s">
         <v>408</v>
       </c>
-      <c r="B7" s="76"/>
+      <c r="B7" s="77"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="7" t="s">
@@ -20752,11 +20762,11 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="76" t="s">
+      <c r="A15" s="77" t="s">
         <v>414</v>
       </c>
-      <c r="B15" s="76"/>
-      <c r="C15" s="76"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="18" t="str" cm="1">
@@ -21426,44 +21436,44 @@
       </c>
     </row>
     <row r="69" spans="1:17">
-      <c r="A69" s="76" t="s">
+      <c r="A69" s="77" t="s">
         <v>417</v>
       </c>
-      <c r="B69" s="76"/>
-      <c r="C69" s="76"/>
-      <c r="D69" s="76"/>
-      <c r="E69" s="76"/>
-      <c r="F69" s="76"/>
-      <c r="G69" s="76"/>
-      <c r="H69" s="76"/>
-      <c r="I69" s="76"/>
-      <c r="J69" s="76"/>
-      <c r="K69" s="76"/>
-      <c r="L69" s="76"/>
-      <c r="M69" s="76"/>
-      <c r="N69" s="76"/>
-      <c r="O69" s="76"/>
-      <c r="P69" s="76"/>
+      <c r="B69" s="77"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="77"/>
+      <c r="E69" s="77"/>
+      <c r="F69" s="77"/>
+      <c r="G69" s="77"/>
+      <c r="H69" s="77"/>
+      <c r="I69" s="77"/>
+      <c r="J69" s="77"/>
+      <c r="K69" s="77"/>
+      <c r="L69" s="77"/>
+      <c r="M69" s="77"/>
+      <c r="N69" s="77"/>
+      <c r="O69" s="77"/>
+      <c r="P69" s="77"/>
     </row>
     <row r="70" spans="1:17">
-      <c r="A70" s="78" t="s">
+      <c r="A70" s="79" t="s">
         <v>418</v>
       </c>
-      <c r="B70" s="79"/>
-      <c r="C70" s="79"/>
-      <c r="D70" s="79"/>
-      <c r="E70" s="79"/>
-      <c r="F70" s="79"/>
-      <c r="G70" s="79"/>
-      <c r="H70" s="79"/>
-      <c r="I70" s="79"/>
-      <c r="J70" s="79"/>
-      <c r="K70" s="79"/>
-      <c r="L70" s="79"/>
-      <c r="M70" s="79"/>
-      <c r="N70" s="79"/>
-      <c r="O70" s="79"/>
-      <c r="P70" s="80"/>
+      <c r="B70" s="80"/>
+      <c r="C70" s="80"/>
+      <c r="D70" s="80"/>
+      <c r="E70" s="80"/>
+      <c r="F70" s="80"/>
+      <c r="G70" s="80"/>
+      <c r="H70" s="80"/>
+      <c r="I70" s="80"/>
+      <c r="J70" s="80"/>
+      <c r="K70" s="80"/>
+      <c r="L70" s="80"/>
+      <c r="M70" s="80"/>
+      <c r="N70" s="80"/>
+      <c r="O70" s="80"/>
+      <c r="P70" s="81"/>
       <c r="Q70" s="1"/>
     </row>
     <row r="71" spans="1:17">
@@ -21525,11 +21535,11 @@
       </c>
       <c r="O71" s="7">
         <f ca="1"/>
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="P71" s="7">
         <f ca="1"/>
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
     <row r="72" spans="1:17">
@@ -21591,11 +21601,11 @@
       </c>
       <c r="O72" s="7">
         <f ca="1"/>
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="P72" s="7">
         <f ca="1"/>
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="73" spans="1:17">
@@ -21657,11 +21667,11 @@
       </c>
       <c r="O73" s="7">
         <f ca="1"/>
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="P73" s="7">
         <f ca="1"/>
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="74" spans="1:17">
@@ -21723,11 +21733,11 @@
       </c>
       <c r="O74" s="7">
         <f ca="1"/>
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="P74" s="7">
         <f ca="1"/>
-        <v>747</v>
+        <v>751</v>
       </c>
     </row>
     <row r="75" spans="1:17">
@@ -21789,11 +21799,11 @@
       </c>
       <c r="O75" s="7">
         <f ca="1"/>
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="P75" s="7">
         <f ca="1"/>
-        <v>747</v>
+        <v>751</v>
       </c>
     </row>
     <row r="76" spans="1:17">
@@ -21855,11 +21865,11 @@
       </c>
       <c r="O76" s="7">
         <f ca="1"/>
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="P76" s="7">
         <f ca="1"/>
-        <v>745</v>
+        <v>749</v>
       </c>
     </row>
     <row r="77" spans="1:17">
@@ -21921,11 +21931,11 @@
       </c>
       <c r="O77" s="7">
         <f ca="1"/>
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="P77" s="7">
         <f ca="1"/>
-        <v>745</v>
+        <v>749</v>
       </c>
     </row>
     <row r="78" spans="1:17">
@@ -21987,11 +21997,11 @@
       </c>
       <c r="O78" s="7">
         <f ca="1"/>
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="P78" s="7">
         <f ca="1"/>
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
     <row r="79" spans="1:17">
@@ -22053,11 +22063,11 @@
       </c>
       <c r="O79" s="7">
         <f ca="1"/>
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="P79" s="7">
         <f ca="1"/>
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="80" spans="1:17">
@@ -22119,11 +22129,11 @@
       </c>
       <c r="O80" s="7">
         <f ca="1"/>
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="P80" s="7">
         <f ca="1"/>
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -22185,11 +22195,11 @@
       </c>
       <c r="O81" s="7">
         <f ca="1"/>
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="P81" s="7">
         <f ca="1"/>
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -22251,11 +22261,11 @@
       </c>
       <c r="O82" s="7">
         <f ca="1"/>
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="P82" s="7">
         <f ca="1"/>
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -22317,11 +22327,11 @@
       </c>
       <c r="O83" s="7">
         <f ca="1"/>
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="P83" s="7">
         <f ca="1"/>
-        <v>717</v>
+        <v>721</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -22383,11 +22393,11 @@
       </c>
       <c r="O84" s="7">
         <f ca="1"/>
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="P84" s="7">
         <f ca="1"/>
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -22449,11 +22459,11 @@
       </c>
       <c r="O85" s="7">
         <f ca="1"/>
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="P85" s="7">
         <f ca="1"/>
-        <v>705</v>
+        <v>709</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -22515,11 +22525,11 @@
       </c>
       <c r="O86" s="7">
         <f ca="1"/>
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="P86" s="7">
         <f ca="1"/>
-        <v>699</v>
+        <v>703</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -22581,11 +22591,11 @@
       </c>
       <c r="O87" s="7">
         <f ca="1"/>
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="P87" s="7">
         <f ca="1"/>
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -22647,11 +22657,11 @@
       </c>
       <c r="O88" s="7">
         <f ca="1"/>
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="P88" s="7">
         <f ca="1"/>
-        <v>696</v>
+        <v>700</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -22713,11 +22723,11 @@
       </c>
       <c r="O89" s="7">
         <f ca="1"/>
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="P89" s="7">
         <f ca="1"/>
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -22779,11 +22789,11 @@
       </c>
       <c r="O90" s="7">
         <f ca="1"/>
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="P90" s="7">
         <f ca="1"/>
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -22845,11 +22855,11 @@
       </c>
       <c r="O91" s="7">
         <f ca="1"/>
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="P91" s="7">
         <f ca="1"/>
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -22911,11 +22921,11 @@
       </c>
       <c r="O92" s="7">
         <f ca="1"/>
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="P92" s="7">
         <f ca="1"/>
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -22977,11 +22987,11 @@
       </c>
       <c r="O93" s="7">
         <f ca="1"/>
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="P93" s="7">
         <f ca="1"/>
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -23043,11 +23053,11 @@
       </c>
       <c r="O94" s="7">
         <f ca="1"/>
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="P94" s="7">
         <f ca="1"/>
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -23109,11 +23119,11 @@
       </c>
       <c r="O95" s="7">
         <f ca="1"/>
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="P95" s="7">
         <f ca="1"/>
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -23175,11 +23185,11 @@
       </c>
       <c r="O96" s="7">
         <f ca="1"/>
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="P96" s="7">
         <f ca="1"/>
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -23241,11 +23251,11 @@
       </c>
       <c r="O97" s="7">
         <f ca="1"/>
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="P97" s="7">
         <f ca="1"/>
-        <v>665</v>
+        <v>669</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -23307,11 +23317,11 @@
       </c>
       <c r="O98" s="7">
         <f ca="1"/>
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="P98" s="7">
         <f ca="1"/>
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -23373,11 +23383,11 @@
       </c>
       <c r="O99" s="7">
         <f ca="1"/>
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="P99" s="7">
         <f ca="1"/>
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -23439,11 +23449,11 @@
       </c>
       <c r="O100" s="7">
         <f ca="1"/>
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="P100" s="7">
         <f ca="1"/>
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -23505,11 +23515,11 @@
       </c>
       <c r="O101" s="7">
         <f ca="1"/>
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="P101" s="7">
         <f ca="1"/>
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -23571,11 +23581,11 @@
       </c>
       <c r="O102" s="7">
         <f ca="1"/>
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="P102" s="7">
         <f ca="1"/>
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -23637,11 +23647,11 @@
       </c>
       <c r="O103" s="7">
         <f ca="1"/>
-        <v>1690</v>
+        <v>1694</v>
       </c>
       <c r="P103" s="7">
         <f ca="1"/>
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -23703,11 +23713,11 @@
       </c>
       <c r="O104" s="7">
         <f ca="1"/>
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="P104" s="7">
         <f ca="1"/>
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -23769,11 +23779,11 @@
       </c>
       <c r="O105" s="7">
         <f ca="1"/>
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="P105" s="7">
         <f ca="1"/>
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -23835,11 +23845,11 @@
       </c>
       <c r="O106" s="7">
         <f ca="1"/>
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="P106" s="7">
         <f ca="1"/>
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -23901,11 +23911,11 @@
       </c>
       <c r="O107" s="7">
         <f ca="1"/>
-        <v>1658</v>
+        <v>1662</v>
       </c>
       <c r="P107" s="7">
         <f ca="1"/>
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -23967,11 +23977,11 @@
       </c>
       <c r="O108" s="7">
         <f ca="1"/>
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="P108" s="7">
         <f ca="1"/>
-        <v>623</v>
+        <v>627</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -24033,11 +24043,11 @@
       </c>
       <c r="O109" s="7">
         <f ca="1"/>
-        <v>1734</v>
+        <v>1738</v>
       </c>
       <c r="P109" s="7">
         <f ca="1"/>
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -24099,11 +24109,11 @@
       </c>
       <c r="O110" s="7">
         <f ca="1"/>
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="P110" s="7">
         <f ca="1"/>
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -24165,11 +24175,11 @@
       </c>
       <c r="O111" s="7">
         <f ca="1"/>
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="P111" s="7">
         <f ca="1"/>
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -24231,11 +24241,11 @@
       </c>
       <c r="O112" s="7">
         <f ca="1"/>
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="P112" s="7">
         <f ca="1"/>
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -24297,11 +24307,11 @@
       </c>
       <c r="O113" s="7">
         <f ca="1"/>
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="P113" s="7">
         <f ca="1"/>
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -24363,11 +24373,11 @@
       </c>
       <c r="O114" s="7">
         <f ca="1"/>
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="P114" s="7">
         <f ca="1"/>
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -24429,11 +24439,11 @@
       </c>
       <c r="O115" s="7">
         <f ca="1"/>
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="P115" s="7">
         <f ca="1"/>
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -24495,11 +24505,11 @@
       </c>
       <c r="O116" s="7">
         <f ca="1"/>
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="P116" s="7">
         <f ca="1"/>
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -24561,11 +24571,11 @@
       </c>
       <c r="O117" s="7">
         <f ca="1"/>
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="P117" s="7">
         <f ca="1"/>
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -24627,11 +24637,11 @@
       </c>
       <c r="O118" s="7">
         <f ca="1"/>
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="P118" s="7">
         <f ca="1"/>
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -24693,11 +24703,11 @@
       </c>
       <c r="O119" s="7">
         <f ca="1"/>
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="P119" s="7">
         <f ca="1"/>
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -24759,11 +24769,11 @@
       </c>
       <c r="O120" s="7">
         <f ca="1"/>
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="P120" s="7">
         <f ca="1"/>
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -24825,11 +24835,11 @@
       </c>
       <c r="O121" s="7">
         <f ca="1"/>
-        <v>1735</v>
+        <v>1739</v>
       </c>
       <c r="P121" s="7">
         <f ca="1"/>
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -24891,11 +24901,11 @@
       </c>
       <c r="O122" s="7">
         <f ca="1"/>
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="P122" s="7">
         <f ca="1"/>
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -24957,11 +24967,11 @@
       </c>
       <c r="O123" s="7">
         <f ca="1"/>
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="P123" s="7">
         <f ca="1"/>
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -25023,11 +25033,11 @@
       </c>
       <c r="O124" s="7">
         <f ca="1"/>
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="P124" s="7">
         <f ca="1"/>
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -25089,11 +25099,11 @@
       </c>
       <c r="O125" s="7">
         <f ca="1"/>
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="P125" s="7">
         <f ca="1"/>
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -25155,11 +25165,11 @@
       </c>
       <c r="O126" s="7">
         <f ca="1"/>
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="P126" s="7">
         <f ca="1"/>
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -25221,11 +25231,11 @@
       </c>
       <c r="O127" s="7">
         <f ca="1"/>
-        <v>1670</v>
+        <v>1674</v>
       </c>
       <c r="P127" s="7">
         <f ca="1"/>
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -25287,11 +25297,11 @@
       </c>
       <c r="O128" s="7">
         <f ca="1"/>
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="P128" s="7">
         <f ca="1"/>
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -25353,11 +25363,11 @@
       </c>
       <c r="O129" s="7">
         <f ca="1"/>
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="P129" s="7">
         <f ca="1"/>
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -25419,11 +25429,11 @@
       </c>
       <c r="O130" s="7">
         <f ca="1"/>
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="P130" s="7">
         <f ca="1"/>
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -25485,11 +25495,11 @@
       </c>
       <c r="O131" s="7">
         <f ca="1"/>
-        <v>1759</v>
+        <v>1763</v>
       </c>
       <c r="P131" s="7">
         <f ca="1"/>
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -25551,11 +25561,11 @@
       </c>
       <c r="O132" s="7">
         <f ca="1"/>
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="P132" s="7">
         <f ca="1"/>
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -25617,11 +25627,11 @@
       </c>
       <c r="O133" s="7">
         <f ca="1"/>
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="P133" s="7">
         <f ca="1"/>
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -25683,11 +25693,11 @@
       </c>
       <c r="O134" s="7">
         <f ca="1"/>
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="P134" s="7">
         <f ca="1"/>
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -25749,11 +25759,11 @@
       </c>
       <c r="O135" s="7">
         <f ca="1"/>
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="P135" s="7">
         <f ca="1"/>
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -25815,11 +25825,11 @@
       </c>
       <c r="O136" s="7">
         <f ca="1"/>
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="P136" s="7">
         <f ca="1"/>
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -25881,11 +25891,11 @@
       </c>
       <c r="O137" s="7">
         <f ca="1"/>
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="P137" s="7">
         <f ca="1"/>
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -25947,11 +25957,11 @@
       </c>
       <c r="O138" s="7">
         <f ca="1"/>
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="P138" s="7">
         <f ca="1"/>
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -26013,11 +26023,11 @@
       </c>
       <c r="O139" s="7">
         <f ca="1"/>
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="P139" s="7">
         <f ca="1"/>
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -26079,11 +26089,11 @@
       </c>
       <c r="O140" s="7">
         <f ca="1"/>
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="P140" s="7">
         <f ca="1"/>
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -26145,11 +26155,11 @@
       </c>
       <c r="O141" s="7">
         <f ca="1"/>
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="P141" s="7">
         <f ca="1"/>
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -26211,11 +26221,11 @@
       </c>
       <c r="O142" s="7">
         <f ca="1"/>
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="P142" s="7">
         <f ca="1"/>
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -26277,11 +26287,11 @@
       </c>
       <c r="O143" s="7">
         <f ca="1"/>
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="P143" s="7">
         <f ca="1"/>
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -26343,11 +26353,11 @@
       </c>
       <c r="O144" s="7">
         <f ca="1"/>
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="P144" s="7">
         <f ca="1"/>
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -26409,11 +26419,11 @@
       </c>
       <c r="O145" s="7">
         <f ca="1"/>
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="P145" s="7">
         <f ca="1"/>
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -26475,11 +26485,11 @@
       </c>
       <c r="O146" s="7">
         <f ca="1"/>
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="P146" s="7">
         <f ca="1"/>
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -26541,11 +26551,11 @@
       </c>
       <c r="O147" s="7">
         <f ca="1"/>
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="P147" s="7">
         <f ca="1"/>
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -26607,11 +26617,11 @@
       </c>
       <c r="O148" s="7">
         <f ca="1"/>
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="P148" s="7">
         <f ca="1"/>
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -26673,11 +26683,11 @@
       </c>
       <c r="O149" s="7">
         <f ca="1"/>
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="P149" s="7">
         <f ca="1"/>
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -26739,11 +26749,11 @@
       </c>
       <c r="O150" s="7">
         <f ca="1"/>
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="P150" s="7">
         <f ca="1"/>
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -26805,11 +26815,11 @@
       </c>
       <c r="O151" s="7">
         <f ca="1"/>
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="P151" s="7">
         <f ca="1"/>
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -26871,11 +26881,11 @@
       </c>
       <c r="O152" s="7">
         <f ca="1"/>
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="P152" s="7">
         <f ca="1"/>
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -26937,11 +26947,11 @@
       </c>
       <c r="O153" s="7">
         <f ca="1"/>
-        <v>1743</v>
+        <v>1747</v>
       </c>
       <c r="P153" s="7">
         <f ca="1"/>
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -27003,11 +27013,11 @@
       </c>
       <c r="O154" s="7">
         <f ca="1"/>
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="P154" s="7">
         <f ca="1"/>
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -27069,11 +27079,11 @@
       </c>
       <c r="O155" s="7">
         <f ca="1"/>
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="P155" s="7">
         <f ca="1"/>
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -27135,11 +27145,11 @@
       </c>
       <c r="O156" s="7">
         <f ca="1"/>
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="P156" s="7">
         <f ca="1"/>
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -27201,11 +27211,11 @@
       </c>
       <c r="O157" s="7">
         <f ca="1"/>
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="P157" s="7">
         <f ca="1"/>
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -27267,11 +27277,11 @@
       </c>
       <c r="O158" s="7">
         <f ca="1"/>
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="P158" s="7">
         <f ca="1"/>
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -27333,11 +27343,11 @@
       </c>
       <c r="O159" s="7">
         <f ca="1"/>
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="P159" s="7">
         <f ca="1"/>
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -27399,11 +27409,11 @@
       </c>
       <c r="O160" s="7">
         <f ca="1"/>
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="P160" s="7">
         <f ca="1"/>
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -27465,11 +27475,11 @@
       </c>
       <c r="O161" s="7">
         <f ca="1"/>
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="P161" s="7">
         <f ca="1"/>
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -27531,11 +27541,11 @@
       </c>
       <c r="O162" s="7">
         <f ca="1"/>
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="P162" s="7">
         <f ca="1"/>
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -27597,11 +27607,11 @@
       </c>
       <c r="O163" s="7">
         <f ca="1"/>
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="P163" s="7">
         <f ca="1"/>
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -27663,11 +27673,11 @@
       </c>
       <c r="O164" s="7">
         <f ca="1"/>
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="P164" s="7">
         <f ca="1"/>
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -27729,19 +27739,19 @@
       </c>
       <c r="O165" s="7">
         <f ca="1"/>
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="P165" s="7">
         <f ca="1"/>
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="167" spans="1:16">
-      <c r="A167" s="76" t="s">
+      <c r="A167" s="77" t="s">
         <v>419</v>
       </c>
-      <c r="B167" s="76"/>
-      <c r="C167" s="76"/>
+      <c r="B167" s="77"/>
+      <c r="C167" s="77"/>
     </row>
     <row r="168" spans="1:16">
       <c r="A168" s="21" t="s">
@@ -28218,7 +28228,7 @@
         <v>No match</v>
       </c>
     </row>
-    <row r="209" spans="1:4">
+    <row r="209" spans="1:6">
       <c r="A209" s="7"/>
       <c r="B209" s="7" t="str">
         <v>Sharon Butler</v>
@@ -28228,15 +28238,15 @@
         <v>No match</v>
       </c>
     </row>
-    <row r="211" spans="1:4">
-      <c r="A211" s="76" t="s">
+    <row r="211" spans="1:6">
+      <c r="A211" s="77" t="s">
         <v>423</v>
       </c>
-      <c r="B211" s="76"/>
-      <c r="C211" s="76"/>
-      <c r="D211" s="76"/>
-    </row>
-    <row r="212" spans="1:4">
+      <c r="B211" s="77"/>
+      <c r="C211" s="77"/>
+      <c r="D211" s="77"/>
+    </row>
+    <row r="212" spans="1:6">
       <c r="A212" s="21" t="s">
         <v>424</v>
       </c>
@@ -28249,8 +28259,9 @@
       <c r="D212" s="21" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="213" spans="1:4">
+      <c r="F212" s="72"/>
+    </row>
+    <row r="213" spans="1:6">
       <c r="A213" s="7" t="str">
         <f>'Raw data'!D2</f>
         <v>Paul Baker</v>
@@ -28268,7 +28279,7 @@
         <v>MON</v>
       </c>
     </row>
-    <row r="214" spans="1:4">
+    <row r="214" spans="1:6">
       <c r="A214" s="7" t="str">
         <f>'Raw data'!D3</f>
         <v>Joseph Jackson</v>
@@ -28286,7 +28297,7 @@
         <v>MON</v>
       </c>
     </row>
-    <row r="215" spans="1:4">
+    <row r="215" spans="1:6">
       <c r="A215" s="7" t="str">
         <f>'Raw data'!D4</f>
         <v>Kevin Scott</v>
@@ -28304,7 +28315,7 @@
         <v>BLE</v>
       </c>
     </row>
-    <row r="216" spans="1:4">
+    <row r="216" spans="1:6">
       <c r="A216" s="7" t="str">
         <f>'Raw data'!D5</f>
         <v>Kathleen Bennett</v>
@@ -28322,7 +28333,7 @@
         <v>BLE</v>
       </c>
     </row>
-    <row r="217" spans="1:4">
+    <row r="217" spans="1:6">
       <c r="A217" s="7" t="str">
         <f>'Raw data'!D6</f>
         <v>Michael Brown</v>
@@ -28340,7 +28351,7 @@
         <v>BOO</v>
       </c>
     </row>
-    <row r="218" spans="1:4">
+    <row r="218" spans="1:6">
       <c r="A218" s="7" t="str">
         <f>'Raw data'!D7</f>
         <v>Dorothy Nelson</v>
@@ -28358,7 +28369,7 @@
         <v>BLE</v>
       </c>
     </row>
-    <row r="219" spans="1:4">
+    <row r="219" spans="1:6">
       <c r="A219" s="7" t="str">
         <f>'Raw data'!D8</f>
         <v>Dorothy Nelson</v>
@@ -28376,7 +28387,7 @@
         <v>HEA</v>
       </c>
     </row>
-    <row r="220" spans="1:4">
+    <row r="220" spans="1:6">
       <c r="A220" s="7" t="str">
         <f>'Raw data'!D9</f>
         <v>Charles Allen</v>
@@ -28394,7 +28405,7 @@
         <v>BLE</v>
       </c>
     </row>
-    <row r="221" spans="1:4">
+    <row r="221" spans="1:6">
       <c r="A221" s="7" t="str">
         <f>'Raw data'!D10</f>
         <v>Robert Thomas</v>
@@ -28412,7 +28423,7 @@
         <v>LAP</v>
       </c>
     </row>
-    <row r="222" spans="1:4">
+    <row r="222" spans="1:6">
       <c r="A222" s="7" t="str">
         <f>'Raw data'!D11</f>
         <v>Karen Hill</v>
@@ -28430,7 +28441,7 @@
         <v>BLE</v>
       </c>
     </row>
-    <row r="223" spans="1:4">
+    <row r="223" spans="1:6">
       <c r="A223" s="7" t="str">
         <f>'Raw data'!D12</f>
         <v>Susan Green</v>
@@ -28448,7 +28459,7 @@
         <v>BOO</v>
       </c>
     </row>
-    <row r="224" spans="1:4">
+    <row r="224" spans="1:6">
       <c r="A224" s="7" t="str">
         <f>'Raw data'!D13</f>
         <v>Kathleen Bennett</v>
@@ -28575,10 +28586,10 @@
       </c>
     </row>
     <row r="232" spans="1:4">
-      <c r="A232" s="76" t="s">
+      <c r="A232" s="77" t="s">
         <v>428</v>
       </c>
-      <c r="B232" s="76"/>
+      <c r="B232" s="77"/>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="7" t="s">
@@ -28586,7 +28597,7 @@
       </c>
       <c r="B233" s="12">
         <f ca="1">NOW()</f>
-        <v>46155.777151620372</v>
+        <v>46159.602401041666</v>
       </c>
     </row>
   </sheetData>
@@ -28632,16 +28643,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="82" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="81"/>
+      <c r="B1" s="82"/>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="83" t="s">
         <v>431</v>
       </c>
-      <c r="B3" s="82"/>
+      <c r="B3" s="83"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="44" t="s">
@@ -28656,7 +28667,7 @@
         <v>433</v>
       </c>
       <c r="B5" s="46">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -28673,14 +28684,14 @@
       </c>
       <c r="B7" s="45">
         <f>B4*B5*(1-B6)</f>
-        <v>2396</v>
+        <v>4792</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="82" t="s">
+      <c r="A11" s="83" t="s">
         <v>478</v>
       </c>
-      <c r="B11" s="82"/>
+      <c r="B11" s="83"/>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="44" t="s">
@@ -29155,10 +29166,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="76" t="s">
         <v>436</v>
       </c>
-      <c r="B1" s="75"/>
+      <c r="B1" s="76"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
@@ -29217,10 +29228,10 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="75" t="s">
+      <c r="A16" s="76" t="s">
         <v>439</v>
       </c>
-      <c r="B16" s="75"/>
+      <c r="B16" s="76"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
@@ -29343,10 +29354,10 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="75" t="s">
+      <c r="A38" s="76" t="s">
         <v>453</v>
       </c>
-      <c r="B38" s="75"/>
+      <c r="B38" s="76"/>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="3" t="s">
@@ -29412,16 +29423,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" customHeight="1">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="84" t="s">
         <v>506</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="88"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="86"/>
     </row>
     <row r="2" spans="1:8" ht="14.4" customHeight="1">
       <c r="A2" s="60"/>
@@ -29434,16 +29445,16 @@
       <c r="H2" s="63"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="84" t="s">
         <v>507</v>
       </c>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="88"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="86"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="61"/>
@@ -29526,16 +29537,16 @@
       <c r="H9" s="63"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="84" t="s">
         <v>509</v>
       </c>
-      <c r="B10" s="87"/>
-      <c r="C10" s="87"/>
-      <c r="D10" s="87"/>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="88"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="86"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="61"/>
@@ -29654,136 +29665,131 @@
       <c r="H17" s="63"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="85" t="s">
+      <c r="A18" s="89" t="s">
         <v>511</v>
       </c>
-      <c r="B18" s="85"/>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="89"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="62">
         <v>1</v>
       </c>
-      <c r="B19" s="83" t="s">
+      <c r="B19" s="87" t="s">
         <v>512</v>
       </c>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
       <c r="H19" s="63"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="62">
         <v>2</v>
       </c>
-      <c r="B20" s="83" t="s">
+      <c r="B20" s="87" t="s">
         <v>513</v>
       </c>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="83"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
       <c r="H20" s="63"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="62">
         <v>3</v>
       </c>
-      <c r="B21" s="83" t="s">
+      <c r="B21" s="87" t="s">
         <v>514</v>
       </c>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
       <c r="H21" s="63"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="62">
         <v>4</v>
       </c>
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="87" t="s">
         <v>515</v>
       </c>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="83"/>
-      <c r="G22" s="83"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="87"/>
       <c r="H22" s="63"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="62">
         <v>5</v>
       </c>
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="87" t="s">
         <v>516</v>
       </c>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="87"/>
+      <c r="F23" s="87"/>
+      <c r="G23" s="87"/>
       <c r="H23" s="63"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="62">
         <v>6</v>
       </c>
-      <c r="B24" s="83" t="s">
+      <c r="B24" s="87" t="s">
         <v>517</v>
       </c>
-      <c r="C24" s="83"/>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="87"/>
       <c r="H24" s="63"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="62">
         <v>7</v>
       </c>
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="87" t="s">
         <v>518</v>
       </c>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
       <c r="H25" s="63"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="64">
         <v>8</v>
       </c>
-      <c r="B26" s="84" t="s">
+      <c r="B26" s="88" t="s">
         <v>519</v>
       </c>
-      <c r="C26" s="84"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
-      <c r="F26" s="84"/>
-      <c r="G26" s="84"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="88"/>
       <c r="H26" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B24:G24"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="A18:H18"/>
@@ -29791,6 +29797,11 @@
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B21:G21"/>
     <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B24:G24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29931,11 +29942,11 @@
       </c>
       <c r="O2" s="47">
         <f ca="1">TODAY()-M2</f>
-        <v>1730</v>
+        <v>1734</v>
       </c>
       <c r="P2" s="47">
         <f ca="1">TODAY()-B2</f>
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="Q2" s="71" t="str">
         <f>TEXT(B2,"yyyy-mm")</f>
@@ -29991,11 +30002,11 @@
       </c>
       <c r="O3" s="47">
         <f t="shared" ref="O3:O66" ca="1" si="0">TODAY()-M3</f>
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="P3" s="47">
         <f t="shared" ref="P3:P66" ca="1" si="1">TODAY()-B3</f>
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="Q3" s="71" t="str">
         <f t="shared" ref="Q3:Q66" si="2">TEXT(B3,"yyyy-mm")</f>
@@ -30051,11 +30062,11 @@
       </c>
       <c r="O4" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="P4" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="Q4" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30111,11 +30122,11 @@
       </c>
       <c r="O5" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="P5" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="Q5" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30171,11 +30182,11 @@
       </c>
       <c r="O6" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="P6" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="Q6" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30231,11 +30242,11 @@
       </c>
       <c r="O7" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="P7" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="Q7" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30291,11 +30302,11 @@
       </c>
       <c r="O8" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1737</v>
+        <v>1741</v>
       </c>
       <c r="P8" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="Q8" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30351,11 +30362,11 @@
       </c>
       <c r="O9" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="P9" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="Q9" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30411,11 +30422,11 @@
       </c>
       <c r="O10" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="P10" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="Q10" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30471,11 +30482,11 @@
       </c>
       <c r="O11" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="P11" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="Q11" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30531,11 +30542,11 @@
       </c>
       <c r="O12" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="P12" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="Q12" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30591,11 +30602,11 @@
       </c>
       <c r="O13" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="P13" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="Q13" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30651,11 +30662,11 @@
       </c>
       <c r="O14" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="P14" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="Q14" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30711,11 +30722,11 @@
       </c>
       <c r="O15" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="P15" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="Q15" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30771,11 +30782,11 @@
       </c>
       <c r="O16" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="P16" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="Q16" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30831,11 +30842,11 @@
       </c>
       <c r="O17" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="P17" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="Q17" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30891,11 +30902,11 @@
       </c>
       <c r="O18" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="P18" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="Q18" s="71" t="str">
         <f t="shared" si="2"/>
@@ -30951,11 +30962,11 @@
       </c>
       <c r="O19" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="P19" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="Q19" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31011,11 +31022,11 @@
       </c>
       <c r="O20" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="P20" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="Q20" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31071,11 +31082,11 @@
       </c>
       <c r="O21" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="P21" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="Q21" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31131,11 +31142,11 @@
       </c>
       <c r="O22" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="P22" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="Q22" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31191,11 +31202,11 @@
       </c>
       <c r="O23" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1746</v>
+        <v>1750</v>
       </c>
       <c r="P23" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="Q23" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31251,11 +31262,11 @@
       </c>
       <c r="O24" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1687</v>
+        <v>1691</v>
       </c>
       <c r="P24" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="Q24" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31311,11 +31322,11 @@
       </c>
       <c r="O25" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="P25" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="Q25" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31371,11 +31382,11 @@
       </c>
       <c r="O26" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="P26" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="Q26" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31431,11 +31442,11 @@
       </c>
       <c r="O27" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="P27" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="Q27" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31491,11 +31502,11 @@
       </c>
       <c r="O28" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="P28" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="Q28" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31551,11 +31562,11 @@
       </c>
       <c r="O29" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="P29" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="Q29" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31611,11 +31622,11 @@
       </c>
       <c r="O30" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="P30" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="Q30" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31671,11 +31682,11 @@
       </c>
       <c r="O31" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="P31" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="Q31" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31731,11 +31742,11 @@
       </c>
       <c r="O32" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1743</v>
+        <v>1747</v>
       </c>
       <c r="P32" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="Q32" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31791,11 +31802,11 @@
       </c>
       <c r="O33" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="P33" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="Q33" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31851,11 +31862,11 @@
       </c>
       <c r="O34" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="P34" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="Q34" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31911,11 +31922,11 @@
       </c>
       <c r="O35" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="P35" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="Q35" s="71" t="str">
         <f t="shared" si="2"/>
@@ -31971,11 +31982,11 @@
       </c>
       <c r="O36" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="P36" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="Q36" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32031,11 +32042,11 @@
       </c>
       <c r="O37" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="P37" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="Q37" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32091,11 +32102,11 @@
       </c>
       <c r="O38" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="P38" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="Q38" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32151,11 +32162,11 @@
       </c>
       <c r="O39" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1748</v>
+        <v>1752</v>
       </c>
       <c r="P39" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="Q39" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32211,11 +32222,11 @@
       </c>
       <c r="O40" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="P40" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="Q40" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32271,11 +32282,11 @@
       </c>
       <c r="O41" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1238</v>
+        <v>1242</v>
       </c>
       <c r="P41" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="Q41" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32331,11 +32342,11 @@
       </c>
       <c r="O42" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="P42" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="Q42" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32391,11 +32402,11 @@
       </c>
       <c r="O43" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="P43" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="Q43" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32451,11 +32462,11 @@
       </c>
       <c r="O44" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="P44" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="Q44" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32511,11 +32522,11 @@
       </c>
       <c r="O45" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="P45" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="Q45" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32571,11 +32582,11 @@
       </c>
       <c r="O46" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="P46" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="Q46" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32631,11 +32642,11 @@
       </c>
       <c r="O47" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="P47" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="Q47" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32691,11 +32702,11 @@
       </c>
       <c r="O48" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1720</v>
+        <v>1724</v>
       </c>
       <c r="P48" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="Q48" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32751,11 +32762,11 @@
       </c>
       <c r="O49" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="P49" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="Q49" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32811,11 +32822,11 @@
       </c>
       <c r="O50" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="P50" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="Q50" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32871,11 +32882,11 @@
       </c>
       <c r="O51" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="P51" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="Q51" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32931,11 +32942,11 @@
       </c>
       <c r="O52" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="P52" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="Q52" s="71" t="str">
         <f t="shared" si="2"/>
@@ -32991,11 +33002,11 @@
       </c>
       <c r="O53" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="P53" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="Q53" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33051,11 +33062,11 @@
       </c>
       <c r="O54" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="P54" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="Q54" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33111,11 +33122,11 @@
       </c>
       <c r="O55" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="P55" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="Q55" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33171,11 +33182,11 @@
       </c>
       <c r="O56" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="P56" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="Q56" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33231,11 +33242,11 @@
       </c>
       <c r="O57" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1717</v>
+        <v>1721</v>
       </c>
       <c r="P57" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="Q57" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33291,11 +33302,11 @@
       </c>
       <c r="O58" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="P58" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="Q58" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33351,11 +33362,11 @@
       </c>
       <c r="O59" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="P59" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="Q59" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33411,11 +33422,11 @@
       </c>
       <c r="O60" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="P60" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="Q60" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33471,11 +33482,11 @@
       </c>
       <c r="O61" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="P61" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="Q61" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33531,11 +33542,11 @@
       </c>
       <c r="O62" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="P62" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="Q62" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33591,11 +33602,11 @@
       </c>
       <c r="O63" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="P63" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="Q63" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33651,11 +33662,11 @@
       </c>
       <c r="O64" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="P64" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="Q64" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33711,11 +33722,11 @@
       </c>
       <c r="O65" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>1734</v>
+        <v>1738</v>
       </c>
       <c r="P65" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="Q65" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33771,11 +33782,11 @@
       </c>
       <c r="O66" s="47">
         <f t="shared" ca="1" si="0"/>
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="P66" s="47">
         <f t="shared" ca="1" si="1"/>
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="Q66" s="71" t="str">
         <f t="shared" si="2"/>
@@ -33831,11 +33842,11 @@
       </c>
       <c r="O67" s="47">
         <f t="shared" ref="O67:O130" ca="1" si="4">TODAY()-M67</f>
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="P67" s="47">
         <f t="shared" ref="P67:P130" ca="1" si="5">TODAY()-B67</f>
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="Q67" s="71" t="str">
         <f t="shared" ref="Q67:Q130" si="6">TEXT(B67,"yyyy-mm")</f>
@@ -33891,11 +33902,11 @@
       </c>
       <c r="O68" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1646</v>
+        <v>1650</v>
       </c>
       <c r="P68" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="Q68" s="71" t="str">
         <f t="shared" si="6"/>
@@ -33951,11 +33962,11 @@
       </c>
       <c r="O69" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="P69" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="Q69" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34011,11 +34022,11 @@
       </c>
       <c r="O70" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="P70" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="Q70" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34071,11 +34082,11 @@
       </c>
       <c r="O71" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="P71" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="Q71" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34131,11 +34142,11 @@
       </c>
       <c r="O72" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="P72" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="Q72" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34191,11 +34202,11 @@
       </c>
       <c r="O73" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="P73" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="Q73" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34251,11 +34262,11 @@
       </c>
       <c r="O74" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="P74" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="Q74" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34311,11 +34322,11 @@
       </c>
       <c r="O75" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="P75" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="Q75" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34371,11 +34382,11 @@
       </c>
       <c r="O76" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="P76" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="Q76" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34431,11 +34442,11 @@
       </c>
       <c r="O77" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="P77" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="Q77" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34491,11 +34502,11 @@
       </c>
       <c r="O78" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="P78" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="Q78" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34551,11 +34562,11 @@
       </c>
       <c r="O79" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="P79" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="Q79" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34611,11 +34622,11 @@
       </c>
       <c r="O80" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="P80" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="Q80" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34671,11 +34682,11 @@
       </c>
       <c r="O81" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="P81" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="Q81" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34731,11 +34742,11 @@
       </c>
       <c r="O82" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="P82" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="Q82" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34791,11 +34802,11 @@
       </c>
       <c r="O83" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="P83" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="Q83" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34851,11 +34862,11 @@
       </c>
       <c r="O84" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="P84" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="Q84" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34911,11 +34922,11 @@
       </c>
       <c r="O85" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="P85" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="Q85" s="71" t="str">
         <f t="shared" si="6"/>
@@ -34971,11 +34982,11 @@
       </c>
       <c r="O86" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="P86" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="Q86" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35031,11 +35042,11 @@
       </c>
       <c r="O87" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="P87" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="Q87" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35091,11 +35102,11 @@
       </c>
       <c r="O88" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="P88" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="Q88" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35151,11 +35162,11 @@
       </c>
       <c r="O89" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="P89" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="Q89" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35211,11 +35222,11 @@
       </c>
       <c r="O90" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="P90" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="Q90" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35271,11 +35282,11 @@
       </c>
       <c r="O91" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1690</v>
+        <v>1694</v>
       </c>
       <c r="P91" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="Q91" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35331,11 +35342,11 @@
       </c>
       <c r="O92" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1697</v>
+        <v>1701</v>
       </c>
       <c r="P92" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="Q92" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35391,11 +35402,11 @@
       </c>
       <c r="O93" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="P93" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="Q93" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35451,11 +35462,11 @@
       </c>
       <c r="O94" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="P94" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="Q94" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35511,11 +35522,11 @@
       </c>
       <c r="O95" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1629</v>
+        <v>1633</v>
       </c>
       <c r="P95" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="Q95" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35571,11 +35582,11 @@
       </c>
       <c r="O96" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1581</v>
+        <v>1585</v>
       </c>
       <c r="P96" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="Q96" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35631,11 +35642,11 @@
       </c>
       <c r="O97" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="P97" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="Q97" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35691,11 +35702,11 @@
       </c>
       <c r="O98" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="P98" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="Q98" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35751,11 +35762,11 @@
       </c>
       <c r="O99" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="P99" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="Q99" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35811,11 +35822,11 @@
       </c>
       <c r="O100" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1658</v>
+        <v>1662</v>
       </c>
       <c r="P100" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="Q100" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35871,11 +35882,11 @@
       </c>
       <c r="O101" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="P101" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="Q101" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35931,11 +35942,11 @@
       </c>
       <c r="O102" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1734</v>
+        <v>1738</v>
       </c>
       <c r="P102" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="Q102" s="71" t="str">
         <f t="shared" si="6"/>
@@ -35991,11 +36002,11 @@
       </c>
       <c r="O103" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="P103" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="Q103" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36051,11 +36062,11 @@
       </c>
       <c r="O104" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="P104" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="Q104" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36111,11 +36122,11 @@
       </c>
       <c r="O105" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="P105" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="Q105" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36171,11 +36182,11 @@
       </c>
       <c r="O106" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="P106" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="Q106" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36231,11 +36242,11 @@
       </c>
       <c r="O107" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="P107" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="Q107" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36291,11 +36302,11 @@
       </c>
       <c r="O108" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="P108" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="Q108" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36351,11 +36362,11 @@
       </c>
       <c r="O109" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="P109" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="Q109" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36411,11 +36422,11 @@
       </c>
       <c r="O110" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="P110" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="Q110" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36471,11 +36482,11 @@
       </c>
       <c r="O111" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="P111" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="Q111" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36531,11 +36542,11 @@
       </c>
       <c r="O112" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="P112" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="Q112" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36591,11 +36602,11 @@
       </c>
       <c r="O113" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="P113" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="Q113" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36651,11 +36662,11 @@
       </c>
       <c r="O114" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1697</v>
+        <v>1701</v>
       </c>
       <c r="P114" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="Q114" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36711,11 +36722,11 @@
       </c>
       <c r="O115" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="P115" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="Q115" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36771,11 +36782,11 @@
       </c>
       <c r="O116" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="P116" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="Q116" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36831,11 +36842,11 @@
       </c>
       <c r="O117" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="P117" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="Q117" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36891,11 +36902,11 @@
       </c>
       <c r="O118" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="P118" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="Q118" s="71" t="str">
         <f t="shared" si="6"/>
@@ -36951,11 +36962,11 @@
       </c>
       <c r="O119" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="P119" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="Q119" s="71" t="str">
         <f t="shared" si="6"/>
@@ -37011,11 +37022,11 @@
       </c>
       <c r="O120" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="P120" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="Q120" s="71" t="str">
         <f t="shared" si="6"/>
@@ -37071,11 +37082,11 @@
       </c>
       <c r="O121" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="P121" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="Q121" s="71" t="str">
         <f t="shared" si="6"/>
@@ -37131,11 +37142,11 @@
       </c>
       <c r="O122" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="P122" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="Q122" s="71" t="str">
         <f t="shared" si="6"/>
@@ -37191,11 +37202,11 @@
       </c>
       <c r="O123" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="P123" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="Q123" s="71" t="str">
         <f t="shared" si="6"/>
@@ -37251,11 +37262,11 @@
       </c>
       <c r="O124" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="P124" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="Q124" s="71" t="str">
         <f t="shared" si="6"/>
@@ -37311,11 +37322,11 @@
       </c>
       <c r="O125" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="P125" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="Q125" s="71" t="str">
         <f t="shared" si="6"/>
@@ -37371,11 +37382,11 @@
       </c>
       <c r="O126" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="P126" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="Q126" s="71" t="str">
         <f t="shared" si="6"/>
@@ -37431,11 +37442,11 @@
       </c>
       <c r="O127" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="P127" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="Q127" s="71" t="str">
         <f t="shared" si="6"/>
@@ -37491,11 +37502,11 @@
       </c>
       <c r="O128" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="P128" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="Q128" s="71" t="str">
         <f t="shared" si="6"/>
@@ -37551,11 +37562,11 @@
       </c>
       <c r="O129" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="P129" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="Q129" s="71" t="str">
         <f t="shared" si="6"/>
@@ -37611,11 +37622,11 @@
       </c>
       <c r="O130" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="P130" s="47">
         <f t="shared" ca="1" si="5"/>
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="Q130" s="71" t="str">
         <f t="shared" si="6"/>
@@ -37671,11 +37682,11 @@
       </c>
       <c r="O131" s="47">
         <f t="shared" ref="O131:O194" ca="1" si="8">TODAY()-M131</f>
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="P131" s="47">
         <f t="shared" ref="P131:P194" ca="1" si="9">TODAY()-B131</f>
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="Q131" s="71" t="str">
         <f t="shared" ref="Q131:Q194" si="10">TEXT(B131,"yyyy-mm")</f>
@@ -37731,11 +37742,11 @@
       </c>
       <c r="O132" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="P132" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="Q132" s="71" t="str">
         <f t="shared" si="10"/>
@@ -37791,11 +37802,11 @@
       </c>
       <c r="O133" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="P133" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="Q133" s="71" t="str">
         <f t="shared" si="10"/>
@@ -37851,11 +37862,11 @@
       </c>
       <c r="O134" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1682</v>
+        <v>1686</v>
       </c>
       <c r="P134" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="Q134" s="71" t="str">
         <f t="shared" si="10"/>
@@ -37911,11 +37922,11 @@
       </c>
       <c r="O135" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="P135" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="Q135" s="71" t="str">
         <f t="shared" si="10"/>
@@ -37971,11 +37982,11 @@
       </c>
       <c r="O136" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1520</v>
+        <v>1524</v>
       </c>
       <c r="P136" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="Q136" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38031,11 +38042,11 @@
       </c>
       <c r="O137" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="P137" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="Q137" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38091,11 +38102,11 @@
       </c>
       <c r="O138" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="P138" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="Q138" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38151,11 +38162,11 @@
       </c>
       <c r="O139" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="P139" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="Q139" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38211,11 +38222,11 @@
       </c>
       <c r="O140" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1735</v>
+        <v>1739</v>
       </c>
       <c r="P140" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="Q140" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38271,11 +38282,11 @@
       </c>
       <c r="O141" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="P141" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="Q141" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38331,11 +38342,11 @@
       </c>
       <c r="O142" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="P142" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="Q142" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38391,11 +38402,11 @@
       </c>
       <c r="O143" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="P143" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="Q143" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38451,11 +38462,11 @@
       </c>
       <c r="O144" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="P144" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="Q144" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38511,11 +38522,11 @@
       </c>
       <c r="O145" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="P145" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="Q145" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38571,11 +38582,11 @@
       </c>
       <c r="O146" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="P146" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="Q146" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38631,11 +38642,11 @@
       </c>
       <c r="O147" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="P147" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="Q147" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38691,11 +38702,11 @@
       </c>
       <c r="O148" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="P148" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="Q148" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38751,11 +38762,11 @@
       </c>
       <c r="O149" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="P149" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="Q149" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38811,11 +38822,11 @@
       </c>
       <c r="O150" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1728</v>
+        <v>1732</v>
       </c>
       <c r="P150" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="Q150" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38871,11 +38882,11 @@
       </c>
       <c r="O151" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1595</v>
+        <v>1599</v>
       </c>
       <c r="P151" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="Q151" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38931,11 +38942,11 @@
       </c>
       <c r="O152" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="P152" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="Q152" s="71" t="str">
         <f t="shared" si="10"/>
@@ -38991,11 +39002,11 @@
       </c>
       <c r="O153" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="P153" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="Q153" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39051,11 +39062,11 @@
       </c>
       <c r="O154" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="P154" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="Q154" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39111,11 +39122,11 @@
       </c>
       <c r="O155" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="P155" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="Q155" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39171,11 +39182,11 @@
       </c>
       <c r="O156" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1670</v>
+        <v>1674</v>
       </c>
       <c r="P156" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="Q156" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39231,11 +39242,11 @@
       </c>
       <c r="O157" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="P157" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="Q157" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39291,11 +39302,11 @@
       </c>
       <c r="O158" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="P158" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="Q158" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39351,11 +39362,11 @@
       </c>
       <c r="O159" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="P159" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="Q159" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39411,11 +39422,11 @@
       </c>
       <c r="O160" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="P160" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="Q160" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39471,11 +39482,11 @@
       </c>
       <c r="O161" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1759</v>
+        <v>1763</v>
       </c>
       <c r="P161" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="Q161" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39531,11 +39542,11 @@
       </c>
       <c r="O162" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="P162" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="Q162" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39591,11 +39602,11 @@
       </c>
       <c r="O163" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="P163" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="Q163" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39651,11 +39662,11 @@
       </c>
       <c r="O164" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="P164" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="Q164" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39711,11 +39722,11 @@
       </c>
       <c r="O165" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1749</v>
+        <v>1753</v>
       </c>
       <c r="P165" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="Q165" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39771,11 +39782,11 @@
       </c>
       <c r="O166" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="P166" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="Q166" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39831,11 +39842,11 @@
       </c>
       <c r="O167" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="P167" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="Q167" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39891,11 +39902,11 @@
       </c>
       <c r="O168" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="P168" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="Q168" s="71" t="str">
         <f t="shared" si="10"/>
@@ -39951,11 +39962,11 @@
       </c>
       <c r="O169" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="P169" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="Q169" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40011,11 +40022,11 @@
       </c>
       <c r="O170" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1530</v>
+        <v>1534</v>
       </c>
       <c r="P170" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="Q170" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40071,11 +40082,11 @@
       </c>
       <c r="O171" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="P171" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="Q171" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40131,11 +40142,11 @@
       </c>
       <c r="O172" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="P172" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="Q172" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40191,11 +40202,11 @@
       </c>
       <c r="O173" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="P173" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="Q173" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40251,11 +40262,11 @@
       </c>
       <c r="O174" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="P174" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="Q174" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40311,11 +40322,11 @@
       </c>
       <c r="O175" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="P175" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="Q175" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40371,11 +40382,11 @@
       </c>
       <c r="O176" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="P176" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="Q176" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40431,11 +40442,11 @@
       </c>
       <c r="O177" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="P177" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="Q177" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40491,11 +40502,11 @@
       </c>
       <c r="O178" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="P178" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="Q178" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40551,11 +40562,11 @@
       </c>
       <c r="O179" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="P179" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="Q179" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40611,11 +40622,11 @@
       </c>
       <c r="O180" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="P180" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="Q180" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40671,11 +40682,11 @@
       </c>
       <c r="O181" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="P181" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="Q181" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40731,11 +40742,11 @@
       </c>
       <c r="O182" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="P182" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="Q182" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40791,11 +40802,11 @@
       </c>
       <c r="O183" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1733</v>
+        <v>1737</v>
       </c>
       <c r="P183" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="Q183" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40851,11 +40862,11 @@
       </c>
       <c r="O184" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="P184" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="Q184" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40911,11 +40922,11 @@
       </c>
       <c r="O185" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="P185" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="Q185" s="71" t="str">
         <f t="shared" si="10"/>
@@ -40971,11 +40982,11 @@
       </c>
       <c r="O186" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="P186" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="Q186" s="71" t="str">
         <f t="shared" si="10"/>
@@ -41031,11 +41042,11 @@
       </c>
       <c r="O187" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="P187" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="Q187" s="71" t="str">
         <f t="shared" si="10"/>
@@ -41091,11 +41102,11 @@
       </c>
       <c r="O188" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="P188" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="Q188" s="71" t="str">
         <f t="shared" si="10"/>
@@ -41151,11 +41162,11 @@
       </c>
       <c r="O189" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="P189" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="Q189" s="71" t="str">
         <f t="shared" si="10"/>
@@ -41211,11 +41222,11 @@
       </c>
       <c r="O190" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="P190" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="Q190" s="71" t="str">
         <f t="shared" si="10"/>
@@ -41271,11 +41282,11 @@
       </c>
       <c r="O191" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="P191" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="Q191" s="71" t="str">
         <f t="shared" si="10"/>
@@ -41331,11 +41342,11 @@
       </c>
       <c r="O192" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="P192" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="Q192" s="71" t="str">
         <f t="shared" si="10"/>
@@ -41391,11 +41402,11 @@
       </c>
       <c r="O193" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="P193" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="Q193" s="71" t="str">
         <f t="shared" si="10"/>
@@ -41451,11 +41462,11 @@
       </c>
       <c r="O194" s="47">
         <f t="shared" ca="1" si="8"/>
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="P194" s="47">
         <f t="shared" ca="1" si="9"/>
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="Q194" s="71" t="str">
         <f t="shared" si="10"/>
@@ -41511,11 +41522,11 @@
       </c>
       <c r="O195" s="47">
         <f t="shared" ref="O195:O251" ca="1" si="12">TODAY()-M195</f>
-        <v>1724</v>
+        <v>1728</v>
       </c>
       <c r="P195" s="47">
         <f t="shared" ref="P195:P251" ca="1" si="13">TODAY()-B195</f>
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="Q195" s="71" t="str">
         <f t="shared" ref="Q195:Q251" si="14">TEXT(B195,"yyyy-mm")</f>
@@ -41571,11 +41582,11 @@
       </c>
       <c r="O196" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1760</v>
+        <v>1764</v>
       </c>
       <c r="P196" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="Q196" s="71" t="str">
         <f t="shared" si="14"/>
@@ -41631,11 +41642,11 @@
       </c>
       <c r="O197" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="P197" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="Q197" s="71" t="str">
         <f t="shared" si="14"/>
@@ -41691,11 +41702,11 @@
       </c>
       <c r="O198" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="P198" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="Q198" s="71" t="str">
         <f t="shared" si="14"/>
@@ -41751,11 +41762,11 @@
       </c>
       <c r="O199" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="P199" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="Q199" s="71" t="str">
         <f t="shared" si="14"/>
@@ -41811,11 +41822,11 @@
       </c>
       <c r="O200" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="P200" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="Q200" s="71" t="str">
         <f t="shared" si="14"/>
@@ -41871,11 +41882,11 @@
       </c>
       <c r="O201" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="P201" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="Q201" s="71" t="str">
         <f t="shared" si="14"/>
@@ -41931,11 +41942,11 @@
       </c>
       <c r="O202" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="P202" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="Q202" s="71" t="str">
         <f t="shared" si="14"/>
@@ -41991,11 +42002,11 @@
       </c>
       <c r="O203" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="P203" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="Q203" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42051,11 +42062,11 @@
       </c>
       <c r="O204" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="P204" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="Q204" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42111,11 +42122,11 @@
       </c>
       <c r="O205" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="P205" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="Q205" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42171,11 +42182,11 @@
       </c>
       <c r="O206" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="P206" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="Q206" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42231,11 +42242,11 @@
       </c>
       <c r="O207" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="P207" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="Q207" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42291,11 +42302,11 @@
       </c>
       <c r="O208" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="P208" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="Q208" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42351,11 +42362,11 @@
       </c>
       <c r="O209" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="P209" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="Q209" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42411,11 +42422,11 @@
       </c>
       <c r="O210" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="P210" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="Q210" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42471,11 +42482,11 @@
       </c>
       <c r="O211" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="P211" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="Q211" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42531,11 +42542,11 @@
       </c>
       <c r="O212" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="P212" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="Q212" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42591,11 +42602,11 @@
       </c>
       <c r="O213" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="P213" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="Q213" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42651,11 +42662,11 @@
       </c>
       <c r="O214" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="P214" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="Q214" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42711,11 +42722,11 @@
       </c>
       <c r="O215" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1522</v>
+        <v>1526</v>
       </c>
       <c r="P215" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="Q215" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42771,11 +42782,11 @@
       </c>
       <c r="O216" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="P216" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="Q216" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42831,11 +42842,11 @@
       </c>
       <c r="O217" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="P217" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="Q217" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42891,11 +42902,11 @@
       </c>
       <c r="O218" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="P218" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="Q218" s="71" t="str">
         <f t="shared" si="14"/>
@@ -42951,11 +42962,11 @@
       </c>
       <c r="O219" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="P219" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="Q219" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43011,11 +43022,11 @@
       </c>
       <c r="O220" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="P220" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="Q220" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43071,11 +43082,11 @@
       </c>
       <c r="O221" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1743</v>
+        <v>1747</v>
       </c>
       <c r="P221" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="Q221" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43131,11 +43142,11 @@
       </c>
       <c r="O222" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="P222" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="Q222" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43191,11 +43202,11 @@
       </c>
       <c r="O223" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="P223" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="Q223" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43251,11 +43262,11 @@
       </c>
       <c r="O224" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="P224" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q224" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43311,11 +43322,11 @@
       </c>
       <c r="O225" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="P225" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="Q225" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43371,11 +43382,11 @@
       </c>
       <c r="O226" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="P226" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="Q226" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43431,11 +43442,11 @@
       </c>
       <c r="O227" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="P227" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="Q227" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43491,11 +43502,11 @@
       </c>
       <c r="O228" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="P228" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="Q228" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43551,11 +43562,11 @@
       </c>
       <c r="O229" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="P229" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="Q229" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43611,11 +43622,11 @@
       </c>
       <c r="O230" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="P230" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="Q230" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43671,11 +43682,11 @@
       </c>
       <c r="O231" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="P231" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="Q231" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43731,11 +43742,11 @@
       </c>
       <c r="O232" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="P232" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="Q232" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43791,11 +43802,11 @@
       </c>
       <c r="O233" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="P233" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="Q233" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43851,11 +43862,11 @@
       </c>
       <c r="O234" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="P234" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="Q234" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43911,11 +43922,11 @@
       </c>
       <c r="O235" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="P235" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="Q235" s="71" t="str">
         <f t="shared" si="14"/>
@@ -43971,11 +43982,11 @@
       </c>
       <c r="O236" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="P236" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="Q236" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44031,11 +44042,11 @@
       </c>
       <c r="O237" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="P237" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="Q237" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44091,11 +44102,11 @@
       </c>
       <c r="O238" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="P238" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="Q238" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44151,11 +44162,11 @@
       </c>
       <c r="O239" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="P239" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="Q239" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44211,11 +44222,11 @@
       </c>
       <c r="O240" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1595</v>
+        <v>1599</v>
       </c>
       <c r="P240" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="Q240" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44271,11 +44282,11 @@
       </c>
       <c r="O241" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="P241" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="Q241" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44331,11 +44342,11 @@
       </c>
       <c r="O242" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="P242" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="Q242" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44391,11 +44402,11 @@
       </c>
       <c r="O243" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="P243" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="Q243" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44451,11 +44462,11 @@
       </c>
       <c r="O244" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="P244" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="Q244" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44511,11 +44522,11 @@
       </c>
       <c r="O245" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="P245" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="Q245" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44571,11 +44582,11 @@
       </c>
       <c r="O246" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="P246" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="Q246" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44631,11 +44642,11 @@
       </c>
       <c r="O247" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1644</v>
+        <v>1648</v>
       </c>
       <c r="P247" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="Q247" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44691,11 +44702,11 @@
       </c>
       <c r="O248" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="P248" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="Q248" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44751,11 +44762,11 @@
       </c>
       <c r="O249" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="P249" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="Q249" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44811,11 +44822,11 @@
       </c>
       <c r="O250" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="P250" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="Q250" s="71" t="str">
         <f t="shared" si="14"/>
@@ -44871,11 +44882,11 @@
       </c>
       <c r="O251" s="47">
         <f t="shared" ca="1" si="12"/>
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="P251" s="47">
         <f t="shared" ca="1" si="13"/>
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="Q251" s="71" t="str">
         <f t="shared" si="14"/>
